--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1890-new.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1890-new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B127C638-D84B-4D9A-A11E-2EEAEE886E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBECCF3D-B9C4-4A3A-B991-5295791D489C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1997,7 +1997,7 @@
       <c r="Z8" s="33"/>
       <c r="AA8" s="33"/>
       <c r="AB8" s="38"/>
-      <c r="AD8" s="5">
+      <c r="AD8" s="39">
         <f>B8</f>
         <v>361499</v>
       </c>
